--- a/grupos/5AEV - Estadisticos 20241.xlsx
+++ b/grupos/5AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -158,12 +158,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rodríguez Román Leticia</t>
+  </si>
+  <si>
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
-    <t>Rodríguez Román Leticia</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
@@ -194,15 +194,15 @@
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>LOBATO</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
+    <t>XOTLANIHUA</t>
   </si>
   <si>
     <t>MENDOZA</t>
   </si>
   <si>
+    <t>VERA</t>
+  </si>
+  <si>
     <t>NOLASCO</t>
   </si>
   <si>
@@ -212,7 +212,10 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>ANTONIO</t>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>YOLET</t>
@@ -224,13 +227,16 @@
     <t>ARACELY</t>
   </si>
   <si>
-    <t>FABIAN ALEJANDRO</t>
-  </si>
-  <si>
-    <t>ABDIEL NOE</t>
+    <t>ALEXANDER</t>
   </si>
   <si>
     <t>ERIK OMAR</t>
+  </si>
+  <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
+    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -760,22 +766,22 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>-1</v>
@@ -814,10 +820,10 @@
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -834,13 +840,13 @@
         <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -852,13 +858,13 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <v>8</v>
       </c>
       <c r="AC5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -890,22 +896,22 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>-1</v>
@@ -944,10 +950,10 @@
         <v>7</v>
       </c>
       <c r="AB6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -979,22 +985,22 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>-1</v>
@@ -1024,10 +1030,10 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1036,7 +1042,7 @@
         <v>10</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1068,22 +1074,22 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>-1</v>
@@ -1110,22 +1116,22 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y8">
         <v>8</v>
       </c>
       <c r="Z8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1157,22 +1163,22 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>-1</v>
@@ -1205,13 +1211,13 @@
         <v>8</v>
       </c>
       <c r="Z9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA9">
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>8</v>
@@ -1246,22 +1252,22 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>-1</v>
@@ -1294,13 +1300,13 @@
         <v>8</v>
       </c>
       <c r="Z10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA10">
         <v>8</v>
       </c>
       <c r="AB10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>8</v>
@@ -1335,22 +1341,22 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1424,22 +1430,22 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>-1</v>
@@ -1481,7 +1487,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1513,22 +1519,22 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P13">
         <v>-1</v>
@@ -1555,13 +1561,13 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>8</v>
@@ -1570,7 +1576,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1602,22 +1608,22 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
         <v>-1</v>
@@ -1644,7 +1650,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1656,7 +1662,7 @@
         <v>8</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC14">
         <v>5</v>
@@ -1691,22 +1697,22 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
         <v>-1</v>
@@ -1733,22 +1739,22 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1780,22 +1786,22 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>-1</v>
@@ -1825,7 +1831,7 @@
         <v>5</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>5</v>
@@ -1834,7 +1840,7 @@
         <v>6</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC16">
         <v>7</v>
@@ -1869,22 +1875,22 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>-1</v>
@@ -1923,10 +1929,10 @@
         <v>10</v>
       </c>
       <c r="AB17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -1958,22 +1964,22 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
         <v>-1</v>
@@ -2000,19 +2006,19 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <v>8</v>
       </c>
       <c r="AB18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC18">
         <v>8</v>
@@ -2038,7 +2044,7 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -2047,22 +2053,22 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>-1</v>
@@ -2089,7 +2095,7 @@
         <v>5</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2136,22 +2142,22 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>-1</v>
@@ -2178,13 +2184,13 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <v>10</v>
@@ -2225,22 +2231,22 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>-1</v>
@@ -2267,10 +2273,10 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <v>7</v>
@@ -2282,7 +2288,7 @@
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:29">
@@ -2314,22 +2320,22 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>-1</v>
@@ -2356,19 +2362,19 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <v>10</v>
       </c>
       <c r="AB22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2403,22 +2409,22 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>-1</v>
@@ -2445,7 +2451,7 @@
         <v>5</v>
       </c>
       <c r="X23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y23">
         <v>7</v>
@@ -2492,22 +2498,22 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P24">
         <v>-1</v>
@@ -2534,22 +2540,22 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>7</v>
       </c>
       <c r="AB24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2703,7 +2709,7 @@
         <v>70</v>
       </c>
       <c r="J4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K4">
         <v>95</v>
@@ -2715,16 +2721,16 @@
         <v>80</v>
       </c>
       <c r="N4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O4">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P4">
         <v>70</v>
       </c>
       <c r="Q4">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R4">
         <v>95</v>
@@ -2736,10 +2742,10 @@
         <v>80</v>
       </c>
       <c r="U4">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="V4">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2756,22 +2762,22 @@
         <v>85</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M5">
         <v>85</v>
       </c>
       <c r="O5">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="R5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T5">
         <v>85</v>
       </c>
       <c r="V5">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2803,43 +2809,43 @@
         <v>75</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K6">
         <v>95</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M6">
         <v>85</v>
       </c>
       <c r="N6">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O6">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P6">
         <v>75</v>
       </c>
       <c r="Q6">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R6">
         <v>95</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="T6">
         <v>85</v>
       </c>
       <c r="U6">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="V6">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -2945,7 +2951,7 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M8">
         <v>100</v>
@@ -2954,7 +2960,7 @@
         <v>96</v>
       </c>
       <c r="O8">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P8">
         <v>90</v>
@@ -2966,7 +2972,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -2975,7 +2981,7 @@
         <v>96</v>
       </c>
       <c r="V8">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3087,7 +3093,7 @@
         <v>80</v>
       </c>
       <c r="N10">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -3108,7 +3114,7 @@
         <v>80</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3143,43 +3149,43 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K11">
         <v>95</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M11">
         <v>70</v>
       </c>
       <c r="N11">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O11">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R11">
         <v>95</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="T11">
         <v>70</v>
       </c>
       <c r="U11">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="V11">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3211,13 +3217,13 @@
         <v>90</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K12">
         <v>95</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M12">
         <v>75</v>
@@ -3226,19 +3232,19 @@
         <v>96</v>
       </c>
       <c r="O12">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P12">
         <v>90</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R12">
         <v>95</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="T12">
         <v>75</v>
@@ -3247,7 +3253,7 @@
         <v>96</v>
       </c>
       <c r="V12">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3279,43 +3285,43 @@
         <v>90</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M13">
         <v>70</v>
       </c>
       <c r="N13">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="O13">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P13">
         <v>90</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="T13">
         <v>70</v>
       </c>
       <c r="U13">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="V13">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3359,10 +3365,10 @@
         <v>80</v>
       </c>
       <c r="N14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O14">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P14">
         <v>90</v>
@@ -3380,10 +3386,10 @@
         <v>80</v>
       </c>
       <c r="U14">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="V14">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3415,13 +3421,13 @@
         <v>80</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K15">
         <v>95</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M15">
         <v>80</v>
@@ -3430,19 +3436,19 @@
         <v>96</v>
       </c>
       <c r="O15">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="P15">
         <v>80</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R15">
         <v>95</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T15">
         <v>80</v>
@@ -3451,7 +3457,7 @@
         <v>96</v>
       </c>
       <c r="V15">
-        <v>85</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3483,43 +3489,43 @@
         <v>80</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K16">
         <v>95</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M16">
         <v>80</v>
       </c>
       <c r="N16">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="O16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P16">
         <v>80</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R16">
         <v>95</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="T16">
         <v>80</v>
       </c>
       <c r="U16">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="V16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3551,13 +3557,13 @@
         <v>90</v>
       </c>
       <c r="J17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K17">
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -3572,13 +3578,13 @@
         <v>90</v>
       </c>
       <c r="Q17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="T17">
         <v>100</v>
@@ -3631,7 +3637,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3652,7 +3658,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -3687,43 +3693,43 @@
         <v>80</v>
       </c>
       <c r="J19">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M19">
         <v>75</v>
       </c>
       <c r="N19">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="O19">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P19">
         <v>80</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="R19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="T19">
         <v>75</v>
       </c>
       <c r="U19">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="V19">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3767,7 +3773,7 @@
         <v>100</v>
       </c>
       <c r="N20">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O20">
         <v>100</v>
@@ -3788,7 +3794,7 @@
         <v>100</v>
       </c>
       <c r="U20">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="V20">
         <v>100</v>
@@ -3835,7 +3841,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3856,7 +3862,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -3891,19 +3897,19 @@
         <v>90</v>
       </c>
       <c r="J22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M22">
         <v>100</v>
       </c>
       <c r="N22">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="O22">
         <v>100</v>
@@ -3912,19 +3918,19 @@
         <v>90</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S22">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="T22">
         <v>100</v>
       </c>
       <c r="U22">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -3971,7 +3977,7 @@
         <v>80</v>
       </c>
       <c r="N23">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="O23">
         <v>100</v>
@@ -3992,7 +3998,7 @@
         <v>80</v>
       </c>
       <c r="U23">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4030,7 +4036,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4039,7 +4045,7 @@
         <v>80</v>
       </c>
       <c r="N24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4051,7 +4057,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -4060,7 +4066,7 @@
         <v>80</v>
       </c>
       <c r="U24">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="V24">
         <v>100</v>
@@ -4120,7 +4126,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>46</v>
@@ -4129,19 +4135,19 @@
         <v>20</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4152,28 +4158,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>20</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" s="2">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G3" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4184,7 +4190,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>47</v>
@@ -4193,19 +4199,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G4" s="2">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4237,7 +4243,7 @@
         <v>9.5</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4301,7 +4307,7 @@
         <v>4.8</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4424,13 +4430,13 @@
         <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4447,13 +4453,13 @@
         <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4470,13 +4476,13 @@
         <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4493,13 +4499,13 @@
         <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4516,13 +4522,13 @@
         <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4539,13 +4545,13 @@
         <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4553,7 +4559,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920413</v>
+        <v>22330051920201</v>
       </c>
       <c r="B8" t="s">
         <v>58</v>
@@ -4562,10 +4568,10 @@
         <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
         <v>46</v>
@@ -4576,7 +4582,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920413</v>
+        <v>22330051920201</v>
       </c>
       <c r="B9" t="s">
         <v>58</v>
@@ -4585,13 +4591,13 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4599,7 +4605,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920180</v>
+        <v>22330051920192</v>
       </c>
       <c r="B10" t="s">
         <v>59</v>
@@ -4608,10 +4614,10 @@
         <v>56</v>
       </c>
       <c r="D10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>46</v>
@@ -4622,19 +4628,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920180</v>
+        <v>22330051920371</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
         <v>46</v>
@@ -4645,22 +4651,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920192</v>
+        <v>22330051920202</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12">
         <v>5</v>

--- a/grupos/5AEV - Estadisticos 20241.xlsx
+++ b/grupos/5AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -185,15 +185,9 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
@@ -203,28 +197,16 @@
     <t>VERA</t>
   </si>
   <si>
-    <t>NOLASCO</t>
-  </si>
-  <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
     <t>COLOHUA</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>YOLET</t>
-  </si>
-  <si>
     <t>DAVID</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
   </si>
   <si>
     <t>ALEXANDER</t>
@@ -763,7 +745,7 @@
         <v>8</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>6</v>
@@ -775,7 +757,7 @@
         <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>6</v>
@@ -843,7 +825,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -861,7 +843,7 @@
         <v>8</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC5">
         <v>7</v>
@@ -893,7 +875,7 @@
         <v>6</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -905,7 +887,7 @@
         <v>7</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>8</v>
@@ -935,7 +917,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -982,7 +964,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>9</v>
@@ -994,7 +976,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>10</v>
@@ -1071,7 +1053,7 @@
         <v>7</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
         <v>9</v>
@@ -1083,7 +1065,7 @@
         <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>8</v>
@@ -1125,7 +1107,7 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>9</v>
@@ -1160,7 +1142,7 @@
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>7</v>
@@ -1172,7 +1154,7 @@
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>8</v>
@@ -1202,7 +1184,7 @@
         <v>-1</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1249,7 +1231,7 @@
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>9</v>
@@ -1261,7 +1243,7 @@
         <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>8</v>
@@ -1291,7 +1273,7 @@
         <v>-1</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>9</v>
@@ -1338,7 +1320,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>6</v>
@@ -1350,7 +1332,7 @@
         <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>6</v>
@@ -1427,7 +1409,7 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>5</v>
@@ -1439,7 +1421,7 @@
         <v>5</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
         <v>6</v>
@@ -1469,7 +1451,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X12">
         <v>5</v>
@@ -1481,7 +1463,7 @@
         <v>5</v>
       </c>
       <c r="AA12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12">
         <v>7</v>
@@ -1516,7 +1498,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1528,7 +1510,7 @@
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>6</v>
@@ -1558,7 +1540,7 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1570,7 +1552,7 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB13">
         <v>7</v>
@@ -1605,7 +1587,7 @@
         <v>5</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1617,7 +1599,7 @@
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>9</v>
@@ -1659,7 +1641,7 @@
         <v>5</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14">
         <v>9</v>
@@ -1694,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -1706,7 +1688,7 @@
         <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -1783,7 +1765,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -1795,7 +1777,7 @@
         <v>5</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>6</v>
@@ -1872,7 +1854,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -1884,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>10</v>
@@ -1961,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -1973,7 +1955,7 @@
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>10</v>
@@ -2015,7 +1997,7 @@
         <v>8</v>
       </c>
       <c r="AA18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB18">
         <v>10</v>
@@ -2050,7 +2032,7 @@
         <v>5</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2062,7 +2044,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
         <v>5</v>
@@ -2104,7 +2086,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB19">
         <v>5</v>
@@ -2139,7 +2121,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>10</v>
@@ -2151,7 +2133,7 @@
         <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>10</v>
@@ -2228,7 +2210,7 @@
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>9</v>
@@ -2240,7 +2222,7 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>9</v>
@@ -2317,7 +2299,7 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J22">
         <v>8</v>
@@ -2329,7 +2311,7 @@
         <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>10</v>
@@ -2406,7 +2388,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>7</v>
@@ -2418,7 +2400,7 @@
         <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N23">
         <v>6</v>
@@ -2460,7 +2442,7 @@
         <v>5</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB23">
         <v>7</v>
@@ -2495,7 +2477,7 @@
         <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>9</v>
@@ -2507,7 +2489,7 @@
         <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>6</v>
@@ -2549,7 +2531,7 @@
         <v>6</v>
       </c>
       <c r="AA24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB24">
         <v>7</v>
@@ -2706,7 +2688,7 @@
         <v>75</v>
       </c>
       <c r="I4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J4">
         <v>98</v>
@@ -2718,7 +2700,7 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N4">
         <v>94</v>
@@ -2727,7 +2709,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P4">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Q4">
         <v>98</v>
@@ -2739,7 +2721,7 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U4">
         <v>94</v>
@@ -2765,7 +2747,7 @@
         <v>97.5</v>
       </c>
       <c r="M5">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="O5">
         <v>93.2</v>
@@ -2774,7 +2756,7 @@
         <v>97.5</v>
       </c>
       <c r="T5">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="V5">
         <v>93.2</v>
@@ -2806,7 +2788,7 @@
         <v>85</v>
       </c>
       <c r="I6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>98</v>
@@ -2818,7 +2800,7 @@
         <v>92.5</v>
       </c>
       <c r="M6">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="N6">
         <v>96</v>
@@ -2827,7 +2809,7 @@
         <v>93.2</v>
       </c>
       <c r="P6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="Q6">
         <v>98</v>
@@ -2839,7 +2821,7 @@
         <v>92.5</v>
       </c>
       <c r="T6">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="U6">
         <v>96</v>
@@ -2874,7 +2856,7 @@
         <v>100</v>
       </c>
       <c r="I7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J7">
         <v>100</v>
@@ -2895,7 +2877,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2942,7 +2924,7 @@
         <v>80</v>
       </c>
       <c r="I8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -2963,7 +2945,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P8">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -3022,7 +3004,7 @@
         <v>100</v>
       </c>
       <c r="M9">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="N9">
         <v>96</v>
@@ -3043,7 +3025,7 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>85</v>
+        <v>93.2</v>
       </c>
       <c r="U9">
         <v>96</v>
@@ -3078,7 +3060,7 @@
         <v>100</v>
       </c>
       <c r="I10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -3090,7 +3072,7 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N10">
         <v>98</v>
@@ -3099,7 +3081,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3111,7 +3093,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U10">
         <v>98</v>
@@ -3146,7 +3128,7 @@
         <v>75</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="J11">
         <v>92</v>
@@ -3158,7 +3140,7 @@
         <v>92.5</v>
       </c>
       <c r="M11">
-        <v>70</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N11">
         <v>82</v>
@@ -3167,7 +3149,7 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="Q11">
         <v>92</v>
@@ -3179,7 +3161,7 @@
         <v>92.5</v>
       </c>
       <c r="T11">
-        <v>70</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U11">
         <v>82</v>
@@ -3214,7 +3196,7 @@
         <v>85</v>
       </c>
       <c r="I12">
-        <v>90</v>
+        <v>72.5</v>
       </c>
       <c r="J12">
         <v>92</v>
@@ -3226,7 +3208,7 @@
         <v>92.5</v>
       </c>
       <c r="M12">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="N12">
         <v>96</v>
@@ -3235,7 +3217,7 @@
         <v>93.2</v>
       </c>
       <c r="P12">
-        <v>90</v>
+        <v>72.5</v>
       </c>
       <c r="Q12">
         <v>92</v>
@@ -3247,7 +3229,7 @@
         <v>92.5</v>
       </c>
       <c r="T12">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U12">
         <v>96</v>
@@ -3294,7 +3276,7 @@
         <v>97.5</v>
       </c>
       <c r="M13">
-        <v>70</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N13">
         <v>76</v>
@@ -3315,7 +3297,7 @@
         <v>97.5</v>
       </c>
       <c r="T13">
-        <v>70</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U13">
         <v>76</v>
@@ -3350,7 +3332,7 @@
         <v>85</v>
       </c>
       <c r="I14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -3362,7 +3344,7 @@
         <v>100</v>
       </c>
       <c r="M14">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N14">
         <v>90</v>
@@ -3371,7 +3353,7 @@
         <v>93.2</v>
       </c>
       <c r="P14">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -3383,7 +3365,7 @@
         <v>100</v>
       </c>
       <c r="T14">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U14">
         <v>90</v>
@@ -3418,7 +3400,7 @@
         <v>85</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J15">
         <v>98</v>
@@ -3430,7 +3412,7 @@
         <v>95</v>
       </c>
       <c r="M15">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N15">
         <v>96</v>
@@ -3439,7 +3421,7 @@
         <v>93.2</v>
       </c>
       <c r="P15">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="Q15">
         <v>98</v>
@@ -3451,7 +3433,7 @@
         <v>95</v>
       </c>
       <c r="T15">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U15">
         <v>96</v>
@@ -3486,7 +3468,7 @@
         <v>80</v>
       </c>
       <c r="I16">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="J16">
         <v>98</v>
@@ -3498,7 +3480,7 @@
         <v>92.5</v>
       </c>
       <c r="M16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N16">
         <v>88</v>
@@ -3507,7 +3489,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P16">
-        <v>80</v>
+        <v>82.5</v>
       </c>
       <c r="Q16">
         <v>98</v>
@@ -3519,7 +3501,7 @@
         <v>92.5</v>
       </c>
       <c r="T16">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U16">
         <v>88</v>
@@ -3622,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="J18">
         <v>100</v>
@@ -3643,7 +3625,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -3690,7 +3672,7 @@
         <v>85</v>
       </c>
       <c r="I19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J19">
         <v>92</v>
@@ -3702,7 +3684,7 @@
         <v>92.5</v>
       </c>
       <c r="M19">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="N19">
         <v>82</v>
@@ -3711,7 +3693,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="P19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q19">
         <v>92</v>
@@ -3723,7 +3705,7 @@
         <v>92.5</v>
       </c>
       <c r="T19">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="U19">
         <v>82</v>
@@ -3894,7 +3876,7 @@
         <v>100</v>
       </c>
       <c r="I22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J22">
         <v>98</v>
@@ -3915,7 +3897,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q22">
         <v>98</v>
@@ -3962,7 +3944,7 @@
         <v>100</v>
       </c>
       <c r="I23">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="J23">
         <v>100</v>
@@ -3974,7 +3956,7 @@
         <v>100</v>
       </c>
       <c r="M23">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N23">
         <v>92</v>
@@ -3983,7 +3965,7 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q23">
         <v>100</v>
@@ -3995,7 +3977,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U23">
         <v>92</v>
@@ -4030,7 +4012,7 @@
         <v>100</v>
       </c>
       <c r="I24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J24">
         <v>100</v>
@@ -4042,7 +4024,7 @@
         <v>100</v>
       </c>
       <c r="M24">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N24">
         <v>98</v>
@@ -4051,7 +4033,7 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -4063,7 +4045,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>80</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U24">
         <v>98</v>
@@ -4135,19 +4117,19 @@
         <v>20</v>
       </c>
       <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2">
         <v>11</v>
       </c>
-      <c r="E2">
-        <v>9</v>
-      </c>
       <c r="F2" s="2">
+        <v>45</v>
+      </c>
+      <c r="G2" s="2">
         <v>55</v>
       </c>
-      <c r="G2" s="2">
-        <v>45</v>
-      </c>
       <c r="H2">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4339,7 +4321,7 @@
         <v>0</v>
       </c>
       <c r="H8">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4389,7 +4371,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4421,22 +4403,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920007</v>
+        <v>22330051920188</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4444,16 +4426,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920007</v>
+        <v>22330051920188</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4467,16 +4449,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920188</v>
+        <v>22330051920201</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4490,16 +4472,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920188</v>
+        <v>22330051920201</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4513,22 +4495,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920190</v>
+        <v>22330051920192</v>
       </c>
       <c r="B6" t="s">
         <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4536,22 +4518,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920190</v>
+        <v>22330051920371</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4559,16 +4541,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920201</v>
+        <v>22330051920202</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4577,98 +4559,6 @@
         <v>46</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920201</v>
-      </c>
-      <c r="B9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920192</v>
-      </c>
-      <c r="B10" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" t="s">
-        <v>56</v>
-      </c>
-      <c r="D10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E10" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920371</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" t="s">
-        <v>71</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920202</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F12" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20241.xlsx
+++ b/grupos/5AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -185,6 +185,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
+    <t>COBOS</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -197,6 +212,21 @@
     <t>VERA</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -204,6 +234,21 @@
   </si>
   <si>
     <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARCO</t>
+  </si>
+  <si>
+    <t>YOLET</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
+  </si>
+  <si>
+    <t>VICTOR MANUEL</t>
   </si>
   <si>
     <t>DAVID</t>
@@ -4371,7 +4416,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4403,16 +4448,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920188</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4426,19 +4471,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920188</v>
+        <v>22330051920177</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
         <v>47</v>
@@ -4449,22 +4494,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920201</v>
+        <v>22330051920177</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4472,22 +4517,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920201</v>
+        <v>21330051920007</v>
       </c>
       <c r="B5" t="s">
         <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4495,22 +4540,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920192</v>
+        <v>21330051920007</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4518,22 +4563,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920371</v>
+        <v>21330051920007</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4541,16 +4586,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920202</v>
+        <v>22330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4559,6 +4604,351 @@
         <v>46</v>
       </c>
       <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920190</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920190</v>
+      </c>
+      <c r="B10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920359</v>
+      </c>
+      <c r="B11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" t="s">
+        <v>5</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920359</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" t="s">
+        <v>75</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920359</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920193</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920193</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>76</v>
+      </c>
+      <c r="E15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" t="s">
+        <v>47</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920193</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>22330051920188</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" t="s">
+        <v>46</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920188</v>
+      </c>
+      <c r="B18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920201</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" t="s">
+        <v>70</v>
+      </c>
+      <c r="D19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F19" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920201</v>
+      </c>
+      <c r="B20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920192</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>79</v>
+      </c>
+      <c r="E21" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920371</v>
+      </c>
+      <c r="B22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>22330051920202</v>
+      </c>
+      <c r="B23" t="s">
+        <v>61</v>
+      </c>
+      <c r="C23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D23" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20241.xlsx
+++ b/grupos/5AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -80,6 +80,9 @@
     <t>GONZALEZ ROSAS LEONEL FELIPE</t>
   </si>
   <si>
+    <t>HERNANDEZ ANTONIO LUIS DAVID</t>
+  </si>
+  <si>
     <t>HERNANDEZ ROJAS DAVID</t>
   </si>
   <si>
@@ -161,18 +164,18 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>Marin Arzaba Roberto</t>
+  </si>
+  <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
     <t>Morales Estrada Adilene</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
-    <t>Marin Arzaba Roberto</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -185,12 +188,21 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS DAVID</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>CAMPOS</t>
   </si>
   <si>
-    <t>COBOS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
@@ -200,22 +212,13 @@
     <t>MOLINA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>VERA</t>
+    <t>ALFONSO</t>
   </si>
   <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>NOLASCO</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>CIRUELO</t>
@@ -227,19 +230,13 @@
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>JOSUE GUSTAVO</t>
   </si>
   <si>
     <t>MARCO</t>
   </si>
   <si>
-    <t>YOLET</t>
+    <t>DAVID</t>
   </si>
   <si>
     <t>ARACELY</t>
@@ -249,21 +246,6 @@
   </si>
   <si>
     <t>VICTOR MANUEL</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>ERIK OMAR</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>ERIK</t>
   </si>
 </sst>
 </file>
@@ -625,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC24"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -811,16 +793,16 @@
         <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>-1</v>
@@ -835,13 +817,13 @@
         <v>5</v>
       </c>
       <c r="X4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>7</v>
       </c>
       <c r="Z4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -941,16 +923,16 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
         <v>-1</v>
@@ -962,16 +944,16 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>7</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>7</v>
@@ -1030,16 +1012,16 @@
         <v>10</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T7">
         <v>-1</v>
@@ -1060,7 +1042,7 @@
         <v>10</v>
       </c>
       <c r="Z7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA7">
         <v>10</v>
@@ -1119,16 +1101,16 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>-1</v>
@@ -1143,7 +1125,7 @@
         <v>6</v>
       </c>
       <c r="X8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>8</v>
@@ -1208,16 +1190,16 @@
         <v>8</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>-1</v>
@@ -1297,16 +1279,16 @@
         <v>8</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
         <v>-1</v>
@@ -1344,46 +1326,46 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="G11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="I11">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="J11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="K11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="L11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="M11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="P11">
         <v>-1</v>
@@ -1401,31 +1383,31 @@
         <v>-1</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="X11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="AA11">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="AB11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1433,19 +1415,19 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>7</v>
       </c>
       <c r="E12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12">
         <v>7</v>
@@ -1457,34 +1439,34 @@
         <v>5</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>6</v>
       </c>
       <c r="O12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>-1</v>
@@ -1499,13 +1481,13 @@
         <v>5</v>
       </c>
       <c r="X12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y12">
         <v>7</v>
       </c>
       <c r="Z12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA12">
         <v>7</v>
@@ -1514,7 +1496,7 @@
         <v>7</v>
       </c>
       <c r="AC12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:29">
@@ -1528,10 +1510,10 @@
         <v>5</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13">
         <v>8</v>
@@ -1540,19 +1522,19 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>6</v>
       </c>
       <c r="L13">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1564,16 +1546,16 @@
         <v>8</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>-1</v>
@@ -1585,16 +1567,16 @@
         <v>-1</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>7</v>
       </c>
       <c r="Z13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA13">
         <v>7</v>
@@ -1603,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="AC13">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1611,28 +1593,28 @@
         <v>23</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F14">
         <v>8</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1641,28 +1623,28 @@
         <v>6</v>
       </c>
       <c r="L14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
         <v>-1</v>
@@ -1674,25 +1656,25 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>7</v>
       </c>
       <c r="AB14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AC14">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:29">
@@ -1703,13 +1685,13 @@
         <v>5</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F15">
         <v>8</v>
@@ -1718,13 +1700,13 @@
         <v>8</v>
       </c>
       <c r="H15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I15">
         <v>5</v>
       </c>
       <c r="J15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>6</v>
@@ -1733,25 +1715,25 @@
         <v>7</v>
       </c>
       <c r="M15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>-1</v>
@@ -1763,25 +1745,25 @@
         <v>-1</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1792,19 +1774,19 @@
         <v>5</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D16">
         <v>7</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16">
         <v>7</v>
@@ -1813,34 +1795,34 @@
         <v>5</v>
       </c>
       <c r="J16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>6</v>
       </c>
       <c r="O16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T16">
         <v>-1</v>
@@ -1852,25 +1834,25 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:29">
@@ -1878,58 +1860,58 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>9</v>
       </c>
       <c r="H17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>-1</v>
@@ -1941,25 +1923,25 @@
         <v>-1</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Z17">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA17">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -1976,10 +1958,10 @@
         <v>9</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>9</v>
@@ -1991,13 +1973,13 @@
         <v>6</v>
       </c>
       <c r="J18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K18">
         <v>8</v>
       </c>
       <c r="L18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2006,19 +1988,19 @@
         <v>10</v>
       </c>
       <c r="O18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>-1</v>
@@ -2030,7 +2012,7 @@
         <v>-1</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2039,16 +2021,16 @@
         <v>9</v>
       </c>
       <c r="Z18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB18">
         <v>10</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2056,58 +2038,58 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K19">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>-1</v>
@@ -2119,25 +2101,25 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AB19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2145,58 +2127,58 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E20">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>-1</v>
@@ -2211,22 +2193,22 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z20">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AA20">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AB20">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2237,55 +2219,55 @@
         <v>6</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>9</v>
       </c>
       <c r="E21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21">
         <v>6</v>
       </c>
       <c r="J21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L21">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>9</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>-1</v>
@@ -2300,19 +2282,19 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2323,58 +2305,58 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D22">
         <v>9</v>
       </c>
       <c r="E22">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G22">
         <v>9</v>
       </c>
       <c r="H22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>6</v>
       </c>
       <c r="J22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22">
         <v>6</v>
       </c>
       <c r="L22">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M22">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O22">
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T22">
         <v>-1</v>
@@ -2386,10 +2368,10 @@
         <v>-1</v>
       </c>
       <c r="W22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>8</v>
@@ -2398,10 +2380,10 @@
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AB22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC22">
         <v>9</v>
@@ -2418,52 +2400,52 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>6</v>
       </c>
       <c r="J23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>6</v>
       </c>
       <c r="L23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
         <v>-1</v>
@@ -2475,25 +2457,25 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC23">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:29">
@@ -2507,81 +2489,170 @@
         <v>5</v>
       </c>
       <c r="D24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24">
+        <v>3</v>
+      </c>
+      <c r="F24">
+        <v>7</v>
+      </c>
+      <c r="G24">
+        <v>7</v>
+      </c>
+      <c r="H24">
+        <v>7</v>
+      </c>
+      <c r="I24">
+        <v>6</v>
+      </c>
+      <c r="J24">
+        <v>7</v>
+      </c>
+      <c r="K24">
+        <v>6</v>
+      </c>
+      <c r="L24">
+        <v>8</v>
+      </c>
+      <c r="M24">
+        <v>5</v>
+      </c>
+      <c r="N24">
+        <v>6</v>
+      </c>
+      <c r="O24">
+        <v>7</v>
+      </c>
+      <c r="P24">
+        <v>7</v>
+      </c>
+      <c r="Q24">
+        <v>9</v>
+      </c>
+      <c r="R24">
+        <v>-1</v>
+      </c>
+      <c r="S24">
+        <v>9</v>
+      </c>
+      <c r="T24">
+        <v>-1</v>
+      </c>
+      <c r="U24">
+        <v>-1</v>
+      </c>
+      <c r="V24">
+        <v>-1</v>
+      </c>
+      <c r="W24">
+        <v>6</v>
+      </c>
+      <c r="X24">
+        <v>7</v>
+      </c>
+      <c r="Y24">
+        <v>7</v>
+      </c>
+      <c r="Z24">
+        <v>7</v>
+      </c>
+      <c r="AA24">
+        <v>6</v>
+      </c>
+      <c r="AB24">
+        <v>7</v>
+      </c>
+      <c r="AC24">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>5</v>
+      </c>
+      <c r="D25">
+        <v>8</v>
+      </c>
+      <c r="E25">
         <v>4</v>
       </c>
-      <c r="F24">
-        <v>7</v>
-      </c>
-      <c r="G24">
-        <v>8</v>
-      </c>
-      <c r="H24">
-        <v>8</v>
-      </c>
-      <c r="I24">
-        <v>6</v>
-      </c>
-      <c r="J24">
-        <v>9</v>
-      </c>
-      <c r="K24">
-        <v>6</v>
-      </c>
-      <c r="L24">
-        <v>8</v>
-      </c>
-      <c r="M24">
-        <v>8</v>
-      </c>
-      <c r="N24">
-        <v>6</v>
-      </c>
-      <c r="O24">
-        <v>9</v>
-      </c>
-      <c r="P24">
-        <v>-1</v>
-      </c>
-      <c r="Q24">
-        <v>-1</v>
-      </c>
-      <c r="R24">
-        <v>-1</v>
-      </c>
-      <c r="S24">
-        <v>-1</v>
-      </c>
-      <c r="T24">
-        <v>-1</v>
-      </c>
-      <c r="U24">
-        <v>-1</v>
-      </c>
-      <c r="V24">
-        <v>-1</v>
-      </c>
-      <c r="W24">
-        <v>5</v>
-      </c>
-      <c r="X24">
-        <v>7</v>
-      </c>
-      <c r="Y24">
-        <v>7</v>
-      </c>
-      <c r="Z24">
-        <v>6</v>
-      </c>
-      <c r="AA24">
-        <v>8</v>
-      </c>
-      <c r="AB24">
-        <v>7</v>
-      </c>
-      <c r="AC24">
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>8</v>
+      </c>
+      <c r="H25">
+        <v>8</v>
+      </c>
+      <c r="I25">
+        <v>6</v>
+      </c>
+      <c r="J25">
+        <v>9</v>
+      </c>
+      <c r="K25">
+        <v>6</v>
+      </c>
+      <c r="L25">
+        <v>8</v>
+      </c>
+      <c r="M25">
+        <v>8</v>
+      </c>
+      <c r="N25">
+        <v>6</v>
+      </c>
+      <c r="O25">
+        <v>9</v>
+      </c>
+      <c r="P25">
+        <v>7</v>
+      </c>
+      <c r="Q25">
+        <v>9</v>
+      </c>
+      <c r="R25">
+        <v>-1</v>
+      </c>
+      <c r="S25">
+        <v>9</v>
+      </c>
+      <c r="T25">
+        <v>-1</v>
+      </c>
+      <c r="U25">
+        <v>-1</v>
+      </c>
+      <c r="V25">
+        <v>-1</v>
+      </c>
+      <c r="W25">
+        <v>6</v>
+      </c>
+      <c r="X25">
+        <v>8</v>
+      </c>
+      <c r="Y25">
+        <v>7</v>
+      </c>
+      <c r="Z25">
+        <v>7</v>
+      </c>
+      <c r="AA25">
+        <v>8</v>
+      </c>
+      <c r="AB25">
+        <v>7</v>
+      </c>
+      <c r="AC25">
         <v>9</v>
       </c>
     </row>
@@ -2598,7 +2669,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -2607,7 +2678,7 @@
     <row r="1" spans="1:22">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -2616,7 +2687,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
@@ -2625,7 +2696,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
@@ -2754,10 +2825,10 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P4">
-        <v>75</v>
+        <v>46.9</v>
       </c>
       <c r="Q4">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="R4">
         <v>95</v>
@@ -2769,7 +2840,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="U4">
-        <v>94</v>
+        <v>62.7</v>
       </c>
       <c r="V4">
         <v>88.59999999999999</v>
@@ -2854,22 +2925,22 @@
         <v>93.2</v>
       </c>
       <c r="P6">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q6">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R6">
         <v>95</v>
       </c>
       <c r="S6">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="T6">
         <v>93.2</v>
       </c>
       <c r="U6">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="V6">
         <v>93.2</v>
@@ -2922,7 +2993,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -2937,7 +3008,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -2990,22 +3061,22 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="T8">
         <v>100</v>
       </c>
       <c r="U8">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="V8">
         <v>90.90000000000001</v>
@@ -3058,10 +3129,10 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3073,7 +3144,7 @@
         <v>93.2</v>
       </c>
       <c r="U9">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="V9">
         <v>100</v>
@@ -3126,7 +3197,7 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q10">
         <v>100</v>
@@ -3141,7 +3212,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="U10">
-        <v>98</v>
+        <v>65.3</v>
       </c>
       <c r="V10">
         <v>100</v>
@@ -3152,67 +3223,67 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="L11">
-        <v>92.5</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="O11">
-        <v>88.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>82.5</v>
+        <v>0</v>
       </c>
       <c r="Q11">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R11">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>92.5</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>86.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="V11">
-        <v>88.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3220,7 +3291,7 @@
         <v>21</v>
       </c>
       <c r="B12">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>100</v>
@@ -3232,16 +3303,16 @@
         <v>100</v>
       </c>
       <c r="F12">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <v>84</v>
+      </c>
+      <c r="H12">
         <v>75</v>
       </c>
-      <c r="G12">
-        <v>96</v>
-      </c>
-      <c r="H12">
-        <v>85</v>
-      </c>
       <c r="I12">
-        <v>72.5</v>
+        <v>82.5</v>
       </c>
       <c r="J12">
         <v>92</v>
@@ -3253,34 +3324,34 @@
         <v>92.5</v>
       </c>
       <c r="M12">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="N12">
+        <v>82</v>
+      </c>
+      <c r="O12">
         <v>88.59999999999999</v>
       </c>
-      <c r="N12">
-        <v>96</v>
-      </c>
-      <c r="O12">
-        <v>93.2</v>
-      </c>
       <c r="P12">
-        <v>72.5</v>
+        <v>51.6</v>
       </c>
       <c r="Q12">
-        <v>92</v>
+        <v>92.5</v>
       </c>
       <c r="R12">
         <v>95</v>
       </c>
       <c r="S12">
-        <v>92.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T12">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="U12">
+        <v>54.7</v>
+      </c>
+      <c r="V12">
         <v>88.59999999999999</v>
-      </c>
-      <c r="U12">
-        <v>96</v>
-      </c>
-      <c r="V12">
-        <v>93.2</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3294,58 +3365,58 @@
         <v>100</v>
       </c>
       <c r="D13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E13">
         <v>100</v>
       </c>
       <c r="F13">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G13">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H13">
         <v>85</v>
       </c>
       <c r="I13">
-        <v>90</v>
+        <v>72.5</v>
       </c>
       <c r="J13">
+        <v>92</v>
+      </c>
+      <c r="K13">
+        <v>95</v>
+      </c>
+      <c r="L13">
+        <v>92.5</v>
+      </c>
+      <c r="M13">
+        <v>88.59999999999999</v>
+      </c>
+      <c r="N13">
         <v>96</v>
-      </c>
-      <c r="K13">
-        <v>97.5</v>
-      </c>
-      <c r="L13">
-        <v>97.5</v>
-      </c>
-      <c r="M13">
-        <v>86.40000000000001</v>
-      </c>
-      <c r="N13">
-        <v>76</v>
       </c>
       <c r="O13">
         <v>93.2</v>
       </c>
       <c r="P13">
+        <v>45.3</v>
+      </c>
+      <c r="Q13">
         <v>90</v>
       </c>
-      <c r="Q13">
-        <v>96</v>
-      </c>
       <c r="R13">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="S13">
-        <v>97.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T13">
-        <v>86.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U13">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="V13">
         <v>93.2</v>
@@ -3362,58 +3433,58 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
       </c>
       <c r="F14">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G14">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="H14">
         <v>85</v>
       </c>
       <c r="I14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="L14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M14">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N14">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="O14">
         <v>93.2</v>
       </c>
       <c r="P14">
+        <v>93.8</v>
+      </c>
+      <c r="Q14">
         <v>95</v>
       </c>
-      <c r="Q14">
-        <v>100</v>
-      </c>
       <c r="R14">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="T14">
-        <v>90.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U14">
-        <v>90</v>
+        <v>50.7</v>
       </c>
       <c r="V14">
         <v>93.2</v>
@@ -3424,7 +3495,7 @@
         <v>24</v>
       </c>
       <c r="B15">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>100</v>
@@ -3439,49 +3510,49 @@
         <v>80</v>
       </c>
       <c r="G15">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H15">
         <v>85</v>
       </c>
       <c r="I15">
-        <v>82.5</v>
+        <v>95</v>
       </c>
       <c r="J15">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>95</v>
       </c>
       <c r="L15">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="M15">
         <v>90.90000000000001</v>
       </c>
       <c r="N15">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="O15">
         <v>93.2</v>
       </c>
       <c r="P15">
-        <v>82.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R15">
         <v>95</v>
       </c>
       <c r="S15">
-        <v>95</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T15">
         <v>90.90000000000001</v>
       </c>
       <c r="U15">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="V15">
         <v>93.2</v>
@@ -3510,7 +3581,7 @@
         <v>96</v>
       </c>
       <c r="H16">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I16">
         <v>82.5</v>
@@ -3522,37 +3593,37 @@
         <v>95</v>
       </c>
       <c r="L16">
-        <v>92.5</v>
+        <v>95</v>
       </c>
       <c r="M16">
         <v>90.90000000000001</v>
       </c>
       <c r="N16">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="O16">
-        <v>90.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="P16">
-        <v>82.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q16">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="R16">
         <v>95</v>
       </c>
       <c r="S16">
-        <v>92.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T16">
         <v>90.90000000000001</v>
       </c>
       <c r="U16">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="V16">
-        <v>90.90000000000001</v>
+        <v>93.2</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3560,67 +3631,67 @@
         <v>26</v>
       </c>
       <c r="B17">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E17">
         <v>100</v>
       </c>
       <c r="F17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="G17">
         <v>96</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I17">
-        <v>90</v>
+        <v>82.5</v>
       </c>
       <c r="J17">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="L17">
         <v>92.5</v>
       </c>
       <c r="M17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N17">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="P17">
-        <v>90</v>
+        <v>51.6</v>
       </c>
       <c r="Q17">
-        <v>96</v>
+        <v>93.8</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S17">
-        <v>92.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="T17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U17">
-        <v>96</v>
+        <v>58.7</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3628,7 +3699,7 @@
         <v>27</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C18">
         <v>100</v>
@@ -3649,43 +3720,43 @@
         <v>100</v>
       </c>
       <c r="I18">
-        <v>97.5</v>
+        <v>90</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K18">
         <v>100</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="T18">
         <v>100</v>
       </c>
       <c r="U18">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -3696,7 +3767,7 @@
         <v>28</v>
       </c>
       <c r="B19">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>100</v>
@@ -3708,55 +3779,55 @@
         <v>100</v>
       </c>
       <c r="F19">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="G19">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="H19">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>90</v>
+        <v>97.5</v>
       </c>
       <c r="J19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="O19">
-        <v>84.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="P19">
-        <v>90</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Q19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S19">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="T19">
-        <v>79.5</v>
+        <v>100</v>
       </c>
       <c r="U19">
-        <v>82</v>
+        <v>65.3</v>
       </c>
       <c r="V19">
-        <v>84.09999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -3764,7 +3835,7 @@
         <v>29</v>
       </c>
       <c r="B20">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C20">
         <v>100</v>
@@ -3776,55 +3847,55 @@
         <v>100</v>
       </c>
       <c r="F20">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="G20">
+        <v>84</v>
+      </c>
+      <c r="H20">
+        <v>85</v>
+      </c>
+      <c r="I20">
+        <v>90</v>
+      </c>
+      <c r="J20">
         <v>92</v>
       </c>
-      <c r="H20">
-        <v>100</v>
-      </c>
-      <c r="I20">
-        <v>100</v>
-      </c>
-      <c r="J20">
-        <v>100</v>
-      </c>
       <c r="K20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="L20">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="M20">
-        <v>100</v>
+        <v>79.5</v>
       </c>
       <c r="N20">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="O20">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R20">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T20">
-        <v>100</v>
+        <v>79.5</v>
       </c>
       <c r="U20">
-        <v>94</v>
+        <v>54.7</v>
       </c>
       <c r="V20">
-        <v>100</v>
+        <v>84.09999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3847,7 +3918,7 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="H21">
         <v>100</v>
@@ -3868,7 +3939,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3877,19 +3948,19 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T21">
         <v>100</v>
       </c>
       <c r="U21">
-        <v>98</v>
+        <v>62.7</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -3900,7 +3971,7 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C22">
         <v>100</v>
@@ -3915,49 +3986,49 @@
         <v>100</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J22">
+        <v>100</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+      <c r="L22">
+        <v>100</v>
+      </c>
+      <c r="M22">
+        <v>100</v>
+      </c>
+      <c r="N22">
         <v>98</v>
       </c>
-      <c r="K22">
-        <v>97.5</v>
-      </c>
-      <c r="L22">
-        <v>95</v>
-      </c>
-      <c r="M22">
-        <v>100</v>
-      </c>
-      <c r="N22">
-        <v>86</v>
-      </c>
       <c r="O22">
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>97.5</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>95</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T22">
         <v>100</v>
       </c>
       <c r="U22">
-        <v>86</v>
+        <v>65.3</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -3968,64 +4039,64 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C23">
         <v>100</v>
       </c>
       <c r="D23">
+        <v>100</v>
+      </c>
+      <c r="E23">
+        <v>100</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>92</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
         <v>95</v>
       </c>
-      <c r="E23">
-        <v>100</v>
-      </c>
-      <c r="F23">
-        <v>80</v>
-      </c>
-      <c r="G23">
-        <v>96</v>
-      </c>
-      <c r="H23">
-        <v>100</v>
-      </c>
-      <c r="I23">
-        <v>87.5</v>
-      </c>
       <c r="J23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K23">
+        <v>97.5</v>
+      </c>
+      <c r="L23">
         <v>95</v>
       </c>
-      <c r="L23">
-        <v>100</v>
-      </c>
       <c r="M23">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N23">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="O23">
         <v>100</v>
       </c>
       <c r="P23">
-        <v>87.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R23">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T23">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="U23">
-        <v>92</v>
+        <v>57.3</v>
       </c>
       <c r="V23">
         <v>100</v>
@@ -4036,13 +4107,13 @@
         <v>33</v>
       </c>
       <c r="B24">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E24">
         <v>100</v>
@@ -4051,19 +4122,19 @@
         <v>80</v>
       </c>
       <c r="G24">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H24">
         <v>100</v>
       </c>
       <c r="I24">
+        <v>87.5</v>
+      </c>
+      <c r="J24">
+        <v>100</v>
+      </c>
+      <c r="K24">
         <v>95</v>
-      </c>
-      <c r="J24">
-        <v>100</v>
-      </c>
-      <c r="K24">
-        <v>97.5</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4072,30 +4143,98 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N24">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
+        <v>92.2</v>
+      </c>
+      <c r="Q24">
+        <v>100</v>
+      </c>
+      <c r="R24">
         <v>95</v>
       </c>
-      <c r="Q24">
-        <v>100</v>
-      </c>
-      <c r="R24">
-        <v>97.5</v>
-      </c>
       <c r="S24">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="T24">
         <v>90.90000000000001</v>
       </c>
       <c r="U24">
+        <v>61.3</v>
+      </c>
+      <c r="V24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25">
+        <v>90</v>
+      </c>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25">
+        <v>100</v>
+      </c>
+      <c r="F25">
+        <v>80</v>
+      </c>
+      <c r="G25">
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <v>95</v>
+      </c>
+      <c r="J25">
+        <v>100</v>
+      </c>
+      <c r="K25">
+        <v>97.5</v>
+      </c>
+      <c r="L25">
+        <v>100</v>
+      </c>
+      <c r="M25">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="N25">
         <v>98</v>
       </c>
-      <c r="V24">
+      <c r="O25">
+        <v>100</v>
+      </c>
+      <c r="P25">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Q25">
+        <v>100</v>
+      </c>
+      <c r="R25">
+        <v>97.5</v>
+      </c>
+      <c r="S25">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="T25">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="U25">
+        <v>65.3</v>
+      </c>
+      <c r="V25">
         <v>100</v>
       </c>
     </row>
@@ -4124,31 +4263,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -4156,121 +4295,121 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>45</v>
+        <v>76.2</v>
       </c>
       <c r="G2" s="2">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>60</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>40</v>
+        <v>9.1</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C4">
+        <v>22</v>
+      </c>
+      <c r="D4">
         <v>20</v>
       </c>
-      <c r="D4">
-        <v>15</v>
-      </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>75</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>25</v>
+        <v>4.5</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>21</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" s="2">
-        <v>90.5</v>
+        <v>95.2</v>
       </c>
       <c r="G5" s="2">
-        <v>9.5</v>
+        <v>4.8</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4281,42 +4420,42 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C6">
+        <v>21</v>
+      </c>
+      <c r="D6">
         <v>20</v>
       </c>
-      <c r="D6">
-        <v>19</v>
-      </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>95.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
+      </c>
+      <c r="I6">
         <v>1</v>
       </c>
-      <c r="F6" s="2">
-        <v>95</v>
-      </c>
-      <c r="G6" s="2">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
       <c r="J6" s="2">
-        <v>0</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7">
         <v>21</v>
@@ -4325,22 +4464,22 @@
         <v>20</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
         <v>95.2</v>
       </c>
       <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
         <v>4.8</v>
-      </c>
-      <c r="H7">
-        <v>7.5</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4351,7 +4490,7 @@
         <v>48</v>
       </c>
       <c r="C8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>21</v>
@@ -4360,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -4369,10 +4508,10 @@
         <v>7.8</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
+        <v>4.5</v>
       </c>
     </row>
   </sheetData>
@@ -4382,7 +4521,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4391,22 +4530,142 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>22330051920185</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>22330051920185</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>22330051920185</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>22330051920185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>22330051920185</v>
+      </c>
+      <c r="B6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>22330051920185</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -4416,7 +4675,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4425,22 +4684,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -4448,22 +4707,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920177</v>
+        <v>22330051920356</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C2" t="s">
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4471,22 +4730,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920177</v>
+        <v>22330051920356</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4494,22 +4753,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920177</v>
+        <v>22330051920356</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
         <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4517,22 +4776,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920007</v>
+        <v>22330051920177</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C5" t="s">
         <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
       </c>
       <c r="F5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4540,19 +4799,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920007</v>
+        <v>22330051920188</v>
       </c>
       <c r="B6" t="s">
         <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>47</v>
@@ -4563,19 +4822,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920007</v>
+        <v>22330051920190</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
         <v>73</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F7" t="s">
         <v>47</v>
@@ -4586,22 +4845,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920190</v>
+        <v>22330051920359</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
         <v>74</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4609,346 +4868,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920190</v>
+        <v>22330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>47</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920190</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" t="s">
-        <v>74</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920359</v>
-      </c>
-      <c r="B11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C11" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920359</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920359</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" t="s">
-        <v>75</v>
-      </c>
-      <c r="E13" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" t="s">
-        <v>48</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920193</v>
-      </c>
-      <c r="B14" t="s">
-        <v>59</v>
-      </c>
-      <c r="C14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" t="s">
-        <v>46</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920193</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920193</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>47</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920188</v>
-      </c>
-      <c r="B17" t="s">
-        <v>60</v>
-      </c>
-      <c r="C17" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>46</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920188</v>
-      </c>
-      <c r="B18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>77</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>47</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920201</v>
-      </c>
-      <c r="B19" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920201</v>
-      </c>
-      <c r="B20" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>47</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920192</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>79</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920371</v>
-      </c>
-      <c r="B22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" t="s">
-        <v>80</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>46</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920202</v>
-      </c>
-      <c r="B23" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20241.xlsx
+++ b/grupos/5AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="76">
   <si>
     <t>Materia</t>
   </si>
@@ -167,13 +167,13 @@
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
+    <t>Morales Estrada Adilene</t>
+  </si>
+  <si>
     <t>Marin Arzaba Roberto</t>
-  </si>
-  <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
-    <t>Morales Estrada Adilene</t>
   </si>
   <si>
     <t>NC</t>
@@ -799,7 +799,7 @@
         <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>8</v>
@@ -820,7 +820,7 @@
         <v>6</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <v>6</v>
@@ -858,7 +858,7 @@
         <v>6</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
         <v>-1</v>
@@ -867,7 +867,7 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA5">
         <v>7</v>
@@ -929,7 +929,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>8</v>
@@ -1018,7 +1018,7 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
         <v>9</v>
@@ -1039,7 +1039,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <v>9</v>
@@ -1107,7 +1107,7 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S8">
         <v>8</v>
@@ -1128,7 +1128,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>7</v>
@@ -1196,7 +1196,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
         <v>9</v>
@@ -1217,7 +1217,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z9">
         <v>8</v>
@@ -1285,7 +1285,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>9</v>
@@ -1306,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10">
         <v>8</v>
@@ -1463,7 +1463,7 @@
         <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
         <v>8</v>
@@ -1484,7 +1484,7 @@
         <v>6</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12">
         <v>6</v>
@@ -1552,7 +1552,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13">
         <v>6</v>
@@ -1641,7 +1641,7 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>8</v>
@@ -1730,7 +1730,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>9</v>
@@ -1819,7 +1819,7 @@
         <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>8</v>
@@ -1840,7 +1840,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z16">
         <v>7</v>
@@ -1908,7 +1908,7 @@
         <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>8</v>
@@ -1997,7 +1997,7 @@
         <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>10</v>
@@ -2018,7 +2018,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <v>9</v>
@@ -2086,7 +2086,7 @@
         <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -2107,7 +2107,7 @@
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <v>8</v>
@@ -2175,7 +2175,7 @@
         <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>10</v>
@@ -2196,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <v>6</v>
@@ -2264,7 +2264,7 @@
         <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2353,7 +2353,7 @@
         <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>9</v>
@@ -2374,7 +2374,7 @@
         <v>8</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2442,7 +2442,7 @@
         <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>9</v>
@@ -2463,7 +2463,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <v>7</v>
@@ -2531,7 +2531,7 @@
         <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>9</v>
@@ -2620,7 +2620,7 @@
         <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
         <v>9</v>
@@ -2825,13 +2825,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P4">
-        <v>46.9</v>
+        <v>50</v>
       </c>
       <c r="Q4">
         <v>95</v>
       </c>
       <c r="R4">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2869,7 +2869,7 @@
         <v>93.2</v>
       </c>
       <c r="R5">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T5">
         <v>93.2</v>
@@ -2931,7 +2931,7 @@
         <v>98.8</v>
       </c>
       <c r="R6">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S6">
         <v>95.3</v>
@@ -3067,7 +3067,7 @@
         <v>98.8</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S8">
         <v>92.2</v>
@@ -3333,13 +3333,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P12">
-        <v>51.6</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="Q12">
         <v>92.5</v>
       </c>
       <c r="R12">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S12">
         <v>90.59999999999999</v>
@@ -3407,7 +3407,7 @@
         <v>90</v>
       </c>
       <c r="R13">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S13">
         <v>89.09999999999999</v>
@@ -3475,7 +3475,7 @@
         <v>95</v>
       </c>
       <c r="R14">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S14">
         <v>95.3</v>
@@ -3543,7 +3543,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S15">
         <v>98.40000000000001</v>
@@ -3611,7 +3611,7 @@
         <v>98.8</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S16">
         <v>96.90000000000001</v>
@@ -3673,13 +3673,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P17">
-        <v>51.6</v>
+        <v>82.8</v>
       </c>
       <c r="Q17">
         <v>93.8</v>
       </c>
       <c r="R17">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S17">
         <v>89.09999999999999</v>
@@ -3883,7 +3883,7 @@
         <v>95</v>
       </c>
       <c r="R20">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S20">
         <v>93.8</v>
@@ -4087,7 +4087,7 @@
         <v>95</v>
       </c>
       <c r="R23">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S23">
         <v>93.8</v>
@@ -4155,7 +4155,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="S24">
         <v>98.40000000000001</v>
@@ -4223,7 +4223,7 @@
         <v>100</v>
       </c>
       <c r="R25">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S25">
         <v>98.40000000000001</v>
@@ -4356,13 +4356,13 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
       </c>
       <c r="C4">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D4">
         <v>20</v>
@@ -4371,24 +4371,24 @@
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>90.90000000000001</v>
+        <v>95.2</v>
       </c>
       <c r="G4" s="2">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
@@ -4400,30 +4400,30 @@
         <v>20</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
         <v>95.2</v>
       </c>
       <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
         <v>4.8</v>
-      </c>
-      <c r="H5">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6">
         <v>21</v>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -4452,34 +4452,34 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
       </c>
       <c r="C7">
+        <v>22</v>
+      </c>
+      <c r="D7">
         <v>21</v>
-      </c>
-      <c r="D7">
-        <v>20</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.2</v>
+        <v>95.5</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I7">
         <v>1</v>
       </c>
       <c r="J7" s="2">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -4585,7 +4585,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4605,7 +4605,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4625,7 +4625,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4675,7 +4675,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4719,7 +4719,7 @@
         <v>70</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
         <v>49</v>
@@ -4742,10 +4742,10 @@
         <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4753,22 +4753,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920356</v>
+        <v>22330051920177</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4776,16 +4776,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920177</v>
+        <v>22330051920188</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4799,16 +4799,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920188</v>
+        <v>22330051920190</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4822,22 +4822,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920190</v>
+        <v>22330051920359</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4845,47 +4845,24 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920359</v>
+        <v>22330051920193</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920193</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5AEV - Estadisticos 20241.xlsx
+++ b/grupos/5AEV - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -164,18 +164,18 @@
     <t>Rodríguez Román Leticia</t>
   </si>
   <si>
+    <t>Ramírez Vargas Miranda Alejandra</t>
+  </si>
+  <si>
+    <t>Morales Estrada Adilene</t>
+  </si>
+  <si>
+    <t>Marin Arzaba Roberto</t>
+  </si>
+  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Ramírez Vargas Miranda Alejandra</t>
-  </si>
-  <si>
-    <t>Morales Estrada Adilene</t>
-  </si>
-  <si>
-    <t>Marin Arzaba Roberto</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -188,33 +188,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CAMPOS</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>LUIS DAVID</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>ALFONSO</t>
-  </si>
-  <si>
     <t>CABRERA</t>
   </si>
   <si>
@@ -224,15 +209,9 @@
     <t>CIRUELO</t>
   </si>
   <si>
-    <t>TIZA</t>
-  </si>
-  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>JOSUE GUSTAVO</t>
-  </si>
-  <si>
     <t>MARCO</t>
   </si>
   <si>
@@ -240,9 +219,6 @@
   </si>
   <si>
     <t>ARACELY</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
   </si>
   <si>
     <t>VICTOR MANUEL</t>
@@ -805,13 +781,13 @@
         <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>5</v>
@@ -832,7 +808,7 @@
         <v>7</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:29">
@@ -861,10 +837,10 @@
         <v>6</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -935,13 +911,13 @@
         <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -959,7 +935,7 @@
         <v>7</v>
       </c>
       <c r="AB6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC6">
         <v>7</v>
@@ -1024,13 +1000,13 @@
         <v>9</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1113,13 +1089,13 @@
         <v>8</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>6</v>
@@ -1140,7 +1116,7 @@
         <v>9</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1202,13 +1178,13 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W9">
         <v>7</v>
@@ -1291,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1326,88 +1302,88 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="G11">
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AB11">
         <v>10</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:29">
@@ -1469,13 +1445,13 @@
         <v>8</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>5</v>
@@ -1558,13 +1534,13 @@
         <v>9</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1579,13 +1555,13 @@
         <v>6</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:29">
@@ -1647,13 +1623,13 @@
         <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1736,13 +1712,13 @@
         <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>6</v>
@@ -1760,10 +1736,10 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC15">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1825,13 +1801,13 @@
         <v>8</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1846,7 +1822,7 @@
         <v>7</v>
       </c>
       <c r="AA16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>7</v>
@@ -1914,13 +1890,13 @@
         <v>8</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -1938,7 +1914,7 @@
         <v>6</v>
       </c>
       <c r="AB17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC17">
         <v>7</v>
@@ -2003,13 +1979,13 @@
         <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2027,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="AB18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18">
         <v>9</v>
@@ -2092,13 +2068,13 @@
         <v>10</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>6</v>
@@ -2181,13 +2157,13 @@
         <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>6</v>
@@ -2205,10 +2181,10 @@
         <v>6</v>
       </c>
       <c r="AB20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC20">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:29">
@@ -2270,13 +2246,13 @@
         <v>8</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>6</v>
@@ -2294,7 +2270,7 @@
         <v>10</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -2359,13 +2335,13 @@
         <v>9</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2386,7 +2362,7 @@
         <v>9</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:29">
@@ -2448,13 +2424,13 @@
         <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W23">
         <v>6</v>
@@ -2472,7 +2448,7 @@
         <v>10</v>
       </c>
       <c r="AB23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>9</v>
@@ -2537,13 +2513,13 @@
         <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
@@ -2561,7 +2537,7 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC24">
         <v>7</v>
@@ -2626,13 +2602,13 @@
         <v>9</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
@@ -2653,7 +2629,7 @@
         <v>7</v>
       </c>
       <c r="AC25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2837,13 +2813,13 @@
         <v>100</v>
       </c>
       <c r="T4">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U4">
-        <v>62.7</v>
+        <v>96.3</v>
       </c>
       <c r="V4">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -2872,10 +2848,10 @@
         <v>96.90000000000001</v>
       </c>
       <c r="T5">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="V5">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -2937,13 +2913,13 @@
         <v>95.3</v>
       </c>
       <c r="T6">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="U6">
-        <v>64</v>
+        <v>97.5</v>
       </c>
       <c r="V6">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3008,7 +2984,7 @@
         <v>100</v>
       </c>
       <c r="U7">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="V7">
         <v>100</v>
@@ -3073,13 +3049,13 @@
         <v>92.2</v>
       </c>
       <c r="T8">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="U8">
-        <v>64</v>
+        <v>93.8</v>
       </c>
       <c r="V8">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3141,13 +3117,13 @@
         <v>100</v>
       </c>
       <c r="T9">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
       <c r="U9">
-        <v>64</v>
+        <v>96.3</v>
       </c>
       <c r="V9">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3209,13 +3185,13 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U10">
-        <v>65.3</v>
+        <v>98.8</v>
       </c>
       <c r="V10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3223,67 +3199,67 @@
         <v>20</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11">
         <v>100</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>100</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>93.8</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3345,13 +3321,13 @@
         <v>90.59999999999999</v>
       </c>
       <c r="T12">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="U12">
-        <v>54.7</v>
+        <v>83.8</v>
       </c>
       <c r="V12">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3413,13 +3389,13 @@
         <v>89.09999999999999</v>
       </c>
       <c r="T13">
-        <v>88.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="U13">
-        <v>64</v>
+        <v>87.5</v>
       </c>
       <c r="V13">
-        <v>93.2</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -3481,13 +3457,13 @@
         <v>95.3</v>
       </c>
       <c r="T14">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="U14">
-        <v>50.7</v>
+        <v>83.8</v>
       </c>
       <c r="V14">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3549,13 +3525,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="T15">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U15">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="V15">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -3617,13 +3593,13 @@
         <v>96.90000000000001</v>
       </c>
       <c r="T16">
-        <v>90.90000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="U16">
-        <v>64</v>
+        <v>96.3</v>
       </c>
       <c r="V16">
-        <v>93.2</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -3685,13 +3661,13 @@
         <v>89.09999999999999</v>
       </c>
       <c r="T17">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="U17">
-        <v>58.7</v>
+        <v>83.8</v>
       </c>
       <c r="V17">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3756,7 +3732,7 @@
         <v>100</v>
       </c>
       <c r="U18">
-        <v>64</v>
+        <v>96.3</v>
       </c>
       <c r="V18">
         <v>100</v>
@@ -3824,7 +3800,7 @@
         <v>100</v>
       </c>
       <c r="U19">
-        <v>65.3</v>
+        <v>95</v>
       </c>
       <c r="V19">
         <v>100</v>
@@ -3889,13 +3865,13 @@
         <v>93.8</v>
       </c>
       <c r="T20">
-        <v>79.5</v>
+        <v>82.8</v>
       </c>
       <c r="U20">
-        <v>54.7</v>
+        <v>83.8</v>
       </c>
       <c r="V20">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -3960,7 +3936,7 @@
         <v>100</v>
       </c>
       <c r="U21">
-        <v>62.7</v>
+        <v>93.8</v>
       </c>
       <c r="V21">
         <v>100</v>
@@ -4028,7 +4004,7 @@
         <v>100</v>
       </c>
       <c r="U22">
-        <v>65.3</v>
+        <v>96.3</v>
       </c>
       <c r="V22">
         <v>100</v>
@@ -4093,13 +4069,13 @@
         <v>93.8</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U23">
-        <v>57.3</v>
+        <v>86.3</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4161,13 +4137,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="T24">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U24">
-        <v>61.3</v>
+        <v>90</v>
       </c>
       <c r="V24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4229,13 +4205,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="T25">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U25">
-        <v>65.3</v>
+        <v>97.5</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -4301,62 +4277,62 @@
         <v>21</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2">
         <v>4</v>
       </c>
       <c r="F2" s="2">
-        <v>76.2</v>
+        <v>81</v>
       </c>
       <c r="G2" s="2">
         <v>19</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>48</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>49</v>
@@ -4365,19 +4341,19 @@
         <v>21</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4388,54 +4364,54 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5">
         <v>21</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
@@ -4444,15 +4420,15 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="2">
-        <v>4.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>51</v>
@@ -4461,57 +4437,57 @@
         <v>22</v>
       </c>
       <c r="D7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>6.9</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C8">
         <v>22</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4521,7 +4497,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4548,126 +4524,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920185</v>
-      </c>
-      <c r="B2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920185</v>
-      </c>
-      <c r="B3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920185</v>
-      </c>
-      <c r="B4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920185</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920185</v>
-      </c>
-      <c r="B6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920185</v>
-      </c>
-      <c r="B7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4675,7 +4531,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4707,22 +4563,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920356</v>
+        <v>22330051920177</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" t="s">
         <v>64</v>
       </c>
-      <c r="D2" t="s">
-        <v>70</v>
-      </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4730,22 +4586,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920356</v>
+        <v>22330051920188</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4753,16 +4609,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920177</v>
+        <v>22330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4776,16 +4632,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920188</v>
+        <v>22330051920193</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4794,75 +4650,6 @@
         <v>47</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920190</v>
-      </c>
-      <c r="B6" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>73</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920359</v>
-      </c>
-      <c r="B7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920193</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>
